--- a/Decks/VialIshai.xlsx
+++ b/Decks/VialIshai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88C3AC4-98DF-4CAE-8266-2E8699B1B053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03700AF1-2FF8-4DF3-9225-83263F92B5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BD9B5A5-7A2F-46EE-8105-67E6CDDE9E55}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="118">
   <si>
     <t>Função</t>
   </si>
@@ -362,9 +362,6 @@
     <t>Blasphemous Act</t>
   </si>
   <si>
-    <t>Niv-Mizzet, Visionary</t>
-  </si>
-  <si>
     <t>Game Over</t>
   </si>
   <si>
@@ -381,6 +378,18 @@
   </si>
   <si>
     <t>Batwing Brume</t>
+  </si>
+  <si>
+    <t>Decorum Dissertation</t>
+  </si>
+  <si>
+    <t>Defacing Duskmage // Vandal's Edit</t>
+  </si>
+  <si>
+    <t>Inkshield</t>
+  </si>
+  <si>
+    <t>Monologue Tax</t>
   </si>
 </sst>
 </file>
@@ -776,7 +785,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="5" customWidth="1"/>
   </cols>
@@ -1515,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,13 +1536,13 @@
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,13 +1671,13 @@
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,13 +2187,13 @@
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>98</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F93"/>
     </row>
@@ -2243,10 +2252,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -2312,6 +2321,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Decks/VialIshai.xlsx
+++ b/Decks/VialIshai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03700AF1-2FF8-4DF3-9225-83263F92B5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26745C13-82DE-412D-8A14-E8563B713C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BD9B5A5-7A2F-46EE-8105-67E6CDDE9E55}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -368,15 +368,9 @@
     <t>Blood for the Blood God!</t>
   </si>
   <si>
-    <t>Bruma Etérea</t>
-  </si>
-  <si>
     <t>Mogis, God of Slaughter</t>
   </si>
   <si>
-    <t>Resonation Flute</t>
-  </si>
-  <si>
     <t>Batwing Brume</t>
   </si>
   <si>
@@ -390,6 +384,9 @@
   </si>
   <si>
     <t>Monologue Tax</t>
+  </si>
+  <si>
+    <t>Resonating Lute</t>
   </si>
 </sst>
 </file>
@@ -1524,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,7 +1539,7 @@
         <v>53</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,13 +1608,13 @@
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,7 +1674,7 @@
         <v>62</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2175,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,7 +2190,7 @@
         <v>98</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F93"/>
     </row>
@@ -2252,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">

--- a/Decks/VialIshai.xlsx
+++ b/Decks/VialIshai.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26745C13-82DE-412D-8A14-E8563B713C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138B2CC6-8D13-4BB4-AD9F-2CA878CF88EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BD9B5A5-7A2F-46EE-8105-67E6CDDE9E55}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
   <si>
     <t>Função</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Fellwar Stone</t>
   </si>
   <si>
-    <t>Thought Vessel</t>
-  </si>
-  <si>
     <t>Draw</t>
   </si>
   <si>
@@ -332,9 +329,6 @@
     <t>Dawn Charm</t>
   </si>
   <si>
-    <t>Aetherize</t>
-  </si>
-  <si>
     <t>Riot Control</t>
   </si>
   <si>
@@ -368,9 +362,6 @@
     <t>Blood for the Blood God!</t>
   </si>
   <si>
-    <t>Mogis, God of Slaughter</t>
-  </si>
-  <si>
     <t>Batwing Brume</t>
   </si>
   <si>
@@ -387,6 +378,21 @@
   </si>
   <si>
     <t>Resonating Lute</t>
+  </si>
+  <si>
+    <t>Ethereal Haze</t>
+  </si>
+  <si>
+    <t>Vivi's Persistence</t>
+  </si>
+  <si>
+    <t>Grand Coliseum</t>
+  </si>
+  <si>
+    <t>Cascading Cataracts</t>
+  </si>
+  <si>
+    <t>Illusionist's Gambit</t>
   </si>
 </sst>
 </file>
@@ -861,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -966,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>19</v>
@@ -1128,10 +1134,10 @@
       </c>
       <c r="B23" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>32</v>
@@ -1146,7 +1152,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>34</v>
@@ -1161,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>35</v>
@@ -1521,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1533,787 +1539,787 @@
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D51" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="5" t="b">
         <f>C54&lt;&gt;D54</f>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="D63" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="D73" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D79" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="D85" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F86"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F87"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F88"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F89"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="D98" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2334,7 +2340,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C101</xm:sqref>
+          <xm:sqref>C2:C8 C10:C30 C32:C38 C40:C101</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
